--- a/data/trans_orig/IP19C08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>10229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>18455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64223</t>
+          <t>64284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72594</t>
+          <t>72660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70937</t>
+          <t>71959</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79444</t>
+          <t>79800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138823</t>
+          <t>139406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150758</t>
+          <t>150841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>12240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19120</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97816</t>
+          <t>97821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106208</t>
+          <t>106336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100993</t>
+          <t>101108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108389</t>
+          <t>108964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>202572</t>
+          <t>202322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213308</t>
+          <t>213236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60602</t>
+          <t>60742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67385</t>
+          <t>67289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70161</t>
+          <t>69801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76495</t>
+          <t>76110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133222</t>
+          <t>134247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142523</t>
+          <t>142745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89457</t>
+          <t>90121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95287</t>
+          <t>95279</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>84899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89435</t>
+          <t>89438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176930</t>
+          <t>177129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184441</t>
+          <t>184096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28110</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>24622</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>48048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322820</t>
+          <t>322948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336989</t>
+          <t>336962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336518</t>
+          <t>337109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349818</t>
+          <t>350395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>662495</t>
+          <t>664613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>683718</t>
+          <t>683954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67000</t>
+          <t>67117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73232</t>
+          <t>73236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67739</t>
+          <t>67866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73926</t>
+          <t>73932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138061</t>
+          <t>138289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145812</t>
+          <t>146498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>104600</t>
+          <t>103836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111223</t>
+          <t>111250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106000</t>
+          <t>105895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113293</t>
+          <t>113259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213198</t>
+          <t>213635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>222787</t>
+          <t>222766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66416</t>
+          <t>65953</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73298</t>
+          <t>73288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75912</t>
+          <t>75933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145311</t>
+          <t>144742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152379</t>
+          <t>152443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>83265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91250</t>
+          <t>91238</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>86967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94175</t>
+          <t>94230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173773</t>
+          <t>173827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183970</t>
+          <t>184135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331765</t>
+          <t>332224</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>344030</t>
+          <t>344843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>345870</t>
+          <t>345065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357131</t>
+          <t>357760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>682043</t>
+          <t>681765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699537</t>
+          <t>699455</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59437</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68129</t>
+          <t>68061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65488</t>
+          <t>66010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>72875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129442</t>
+          <t>129095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139972</t>
+          <t>139532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99988</t>
+          <t>99851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105887</t>
+          <t>105911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103244</t>
+          <t>103239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108020</t>
+          <t>108019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205590</t>
+          <t>205558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213020</t>
+          <t>213325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68807</t>
+          <t>69115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>74415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71724</t>
+          <t>71195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76206</t>
+          <t>76209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142637</t>
+          <t>142440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149880</t>
+          <t>150439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102531</t>
+          <t>103526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102351</t>
+          <t>102484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208480</t>
+          <t>208823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>215053</t>
+          <t>215054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21034</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341352</t>
+          <t>341584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353947</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>351861</t>
+          <t>351749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>361856</t>
+          <t>361866</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>697855</t>
+          <t>698205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713164</t>
+          <t>713397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62386</t>
+          <t>62035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>68397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81735</t>
+          <t>81872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145824</t>
+          <t>145650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153071</t>
+          <t>152826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>11175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15214</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106208</t>
+          <t>106568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112884</t>
+          <t>113013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155564</t>
+          <t>156201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165862</t>
+          <t>165926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265895</t>
+          <t>266530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>277486</t>
+          <t>277637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102575</t>
+          <t>101802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97495</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118932</t>
+          <t>119044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201992</t>
+          <t>201641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225086</t>
+          <t>225264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1836</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96737</t>
+          <t>96750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101369</t>
+          <t>102031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>110104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201638</t>
+          <t>201088</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210476</t>
+          <t>210285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>377641</t>
+          <t>376728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387084</t>
+          <t>386795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>452431</t>
+          <t>451611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>475364</t>
+          <t>474928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836087</t>
+          <t>836323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859615</t>
+          <t>859824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C08-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11001</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>6332</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3013</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11389</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11384</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5706</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2388</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10229</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76482</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71187</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69341</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>64284</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72660</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>64289</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72749</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76482</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>71959</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>79800</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139406</t>
+          <t>138834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150841</t>
+          <t>150534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11180</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6998</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3725</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12240</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12029</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5942</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10523</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>105689</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100451</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108982</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103063</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>97821</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>106336</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98032</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>106259</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>105689</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>101108</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108964</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>202322</t>
+          <t>201604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213236</t>
+          <t>213408</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3929</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7852</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4283</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1919</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8466</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8273</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3929</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1759</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8068</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73940</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70017</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76509</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64925</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60742</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67289</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>60935</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>67383</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,81%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>73940</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69801</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76110</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134247</t>
+          <t>133076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142745</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,67 +1757,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5549</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2423</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5868</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6483</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88146</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>84494</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>89438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>93566</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>90121</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>95279</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>89506</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>95276</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,26%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>88146</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>84899</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>89438</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,89%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177129</t>
+          <t>177085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184096</t>
+          <t>184366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11614</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25056</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20035</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13968</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>27982</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14335</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27686</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17473</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11336</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>24622</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48048</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>344258</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>336675</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>350117</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>493</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>330895</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>322948</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>336962</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>323244</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>336595</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,02%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>344258</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>337109</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>350395</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664613</t>
+          <t>664287</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>683954</t>
+          <t>683784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2757</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7376</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71837</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66931</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73904</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>71161</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67117</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73236</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67661</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73250</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71837</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67866</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73932</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138289</t>
+          <t>138302</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146498</t>
+          <t>146114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8258</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>3993</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8763</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8782</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8811</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110582</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106448</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>113306</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>108606</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103836</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>111250</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>103817</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>110627</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110582</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>105895</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>113259</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213635</t>
+          <t>213779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>222766</t>
+          <t>222703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114706</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>112599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>114706</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3534</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1209</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8193</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3820</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78492</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70963</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65953</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>73288</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66304</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73129</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,26%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78492</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75933</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144742</t>
+          <t>144741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152443</t>
+          <t>152254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10174</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4629</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9712</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9815</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9334</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>86127</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94198</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>88348</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83265</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91238</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>83162</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>90895</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>91300</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>86967</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>94230</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173827</t>
+          <t>173157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184135</t>
+          <t>183852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13790</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20159</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>14912</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9148</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21767</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8974</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>22241</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>13790</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>8242</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20937</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>352212</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>345843</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>357269</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>483</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>339079</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>332224</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>344843</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>331750</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>345017</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>352212</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>345065</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>357760</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681765</t>
+          <t>682198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699455</t>
+          <t>699123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366002</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353991</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4372</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9352</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5972</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2780</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10631</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11670</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4372</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8937</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -4735,67 +4735,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>70575</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65595</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73406</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>64869</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60210</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>68061</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59171</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67927</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70575</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>66010</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72875</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129095</t>
+          <t>128963</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139532</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74947</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74947</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>74947</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>74947</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>74947</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>74947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4849</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3593</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7795</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106789</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>103743</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108021</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103590</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>99851</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105911</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99388</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>105658</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>106789</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>103239</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108019</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205558</t>
+          <t>205892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213325</t>
+          <t>213266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2112</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5601</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3175</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1173</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6473</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6486</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5668</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74751</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71262</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76212</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72413</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69115</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74415</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69102</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74382</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74751</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71195</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76209</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142440</t>
+          <t>142170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150439</t>
+          <t>149881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1094</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5481</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5477</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4273</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5764,69 +5764,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>105331</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>101376</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>107913</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>103526</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>103530</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105331</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>102484</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>286</t>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208823</t>
+          <t>208649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9713</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16416</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13833</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8625</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21034</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8650</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20898</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5292</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>15409</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>31894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>357445</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>350742</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>361395</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>348785</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>341584</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>353993</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>341720</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>353968</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>357445</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>351749</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>361866</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>698205</t>
+          <t>697882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>713397</t>
+          <t>713767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>367158</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>367158</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2772</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80696</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78685</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>62035</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>68397</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84248</t>
+          <t>70795</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81872</t>
+          <t>66752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>73172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>150486</t>
+          <t>151491</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145650</t>
+          <t>146761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152826</t>
+          <t>154011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,107 +6907,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11956</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7165</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7491</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>7436</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>14425</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>7577</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>3472</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>14579</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -7020,107 +7020,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>158015</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>150374</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>160977</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>110703</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>106568</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>113013</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>113864</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>109495</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>116173</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>271880</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>264891</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>275835</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>97,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>162829</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>156201</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>165926</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,32%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>273532</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>266530</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>277637</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1168</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21680</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1222</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4144</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20754</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25561</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105970</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>90418</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>110930</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>105733</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>101802</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>101362</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>98295</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>102439</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>114002</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>99493</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>119044</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>82,74%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>265</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>219735</t>
+          <t>207331</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>201641</t>
+          <t>191112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225264</t>
+          <t>212483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9745</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4576</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9540</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>100883</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95464</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>103567</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>100291</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>96750</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>101634</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>96991</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>102575</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>106995</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>102031</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>110104</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>270</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>207287</t>
+          <t>202516</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201088</t>
+          <t>197297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210285</t>
+          <t>205436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15531</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8342</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30526</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8668</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14905</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39753</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>445564</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>430569</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>452753</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>541</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>382965</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>376728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>386795</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>468075</t>
+          <t>387655</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451611</t>
+          <t>381240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474928</t>
+          <t>391850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>851039</t>
+          <t>833218</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836323</t>
+          <t>817064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859824</t>
+          <t>840871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
